--- a/Explainer Demo/Physical Architecture.xlsx
+++ b/Explainer Demo/Physical Architecture.xlsx
@@ -20,9 +20,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t xml:space="preserve">TBD</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t xml:space="preserve">Physical Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System-of-System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole Plane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuselage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propulsion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turbine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Ducting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wing Control Surfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tail Control Surfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actuating Vents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2.1</t>
   </si>
 </sst>
 </file>
@@ -56,12 +191,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -98,8 +239,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -292,15 +445,281 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="2.08"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A3:E3)</f>
+        <v>Whole System</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A4:E4)</f>
+        <v>Whole Plane</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A5:E5)</f>
+        <v>Airframe</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A6:E6)</f>
+        <v>Fuselage</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A7:E7)</f>
+        <v>Wings</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A8:E8)</f>
+        <v>Tail</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A9:E9)</f>
+        <v>Propulsion</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A10:E10)</f>
+        <v>Turbine</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A11:E11)</f>
+        <v>Internal Ducting</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A12:E12)</f>
+        <v>Control</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A13:E13)</f>
+        <v>Wing Control Surfaces</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A14:E14)</f>
+        <v>Tail Control Surfaces</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A15:E15)</f>
+        <v>Actuating Vents</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A16:E16)</f>
+        <v>Computing</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A17:E17)</f>
+        <v>Electrical</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A18:E18)</f>
+        <v>Ground</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A19:E19)</f>
+        <v>Pilot</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A20:E20)</f>
+        <v>Transmitter</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f aca="false">_xlfn.CONCAT(A21:E21)</f>
+        <v>Live Telemetry</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
